--- a/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>SHEL</t>
   </si>
@@ -656,147 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>316620000</v>
+      </c>
+      <c r="E8" s="3">
         <v>381314000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>261504000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>180543000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>344877000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>388379000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>305179000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>233591000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>264960000</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>238123000</v>
+      </c>
+      <c r="E9" s="3">
         <v>284006000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>198734000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>141094000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>279421000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>321369000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>250099000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>191008000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>222739000</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>78497000</v>
+      </c>
+      <c r="E10" s="3">
         <v>97308000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>62770000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39449000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>65456000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>67010000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>55080000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>42583000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>42221000</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,38 +821,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3037000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2787000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2238000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2654000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3316000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2326000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2867000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3122000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6812000</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -868,69 +884,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7927000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3276000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1977000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27177000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1073000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2834000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1048000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1853000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5547000</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>23106000</v>
+      </c>
+      <c r="E15" s="3">
         <v>22393000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22903000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24981000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>25109000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21704000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22033000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>23091000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17707000</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -940,68 +965,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>286345000</v>
+      </c>
+      <c r="E17" s="3">
         <v>319196000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>233676000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>206284000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>320130000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>354827000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>288933000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>230592000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>264718000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>30275000</v>
+      </c>
+      <c r="E18" s="3">
         <v>62118000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>27828000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-25741000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24747000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>33552000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16246000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2999000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>242000</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1014,158 +1046,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>6261000</v>
+      </c>
+      <c r="E20" s="3">
         <v>5442000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5157000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2334000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4578000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4743000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4710000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4614000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2798000</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>86089000</v>
+        <v>55065000</v>
       </c>
       <c r="E21" s="3">
-        <v>59906000</v>
+        <v>94481000</v>
       </c>
       <c r="F21" s="3">
-        <v>29037000</v>
+        <v>85429000</v>
       </c>
       <c r="G21" s="3">
-        <v>58026000</v>
+        <v>5294000</v>
       </c>
       <c r="H21" s="3">
-        <v>60430000</v>
+        <v>51460000</v>
       </c>
       <c r="I21" s="3">
-        <v>47179000</v>
+        <v>64518000</v>
       </c>
       <c r="J21" s="3">
+        <v>45949000</v>
+      </c>
+      <c r="K21" s="3">
         <v>32606000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29754000</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>3909000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2745000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3156000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3560000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3840000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2674000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2826000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2007000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>993000</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>32627000</v>
+      </c>
+      <c r="E23" s="3">
         <v>64815000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>29829000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26967000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>25485000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>35621000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18130000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5606000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2047000</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>12991000</v>
+      </c>
+      <c r="E24" s="3">
         <v>21941000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9199000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5433000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9053000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11715000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2695000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>829000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-153000</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1193,69 +1241,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>19636000</v>
+      </c>
+      <c r="E26" s="3">
         <v>42874000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20630000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21534000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16432000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23906000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15435000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4777000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2200000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>19359000</v>
+      </c>
+      <c r="E27" s="3">
         <v>42309000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20101000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21680000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15842000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>23352000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14977000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4575000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1939000</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1283,9 +1340,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1304,18 +1364,21 @@
       <c r="H29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2000000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1343,9 +1406,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,69 +1439,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6261000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5442000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5157000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2334000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4578000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4743000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4710000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4614000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2798000</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19359000</v>
+      </c>
+      <c r="E33" s="3">
         <v>42309000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20101000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21680000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15842000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>23352000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12977000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4575000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1939000</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1463,74 +1538,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19359000</v>
+      </c>
+      <c r="E35" s="3">
         <v>42309000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20101000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21680000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15842000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23352000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12977000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4575000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1939000</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,8 +1627,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1557,278 +1642,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31724000</v>
+      </c>
+      <c r="E41" s="3">
         <v>34943000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32441000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>61375000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14959000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22829000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16196000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14697000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23786000</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6590000</v>
+      </c>
+      <c r="E42" s="3">
         <v>5147000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4416000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2220000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2665000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3655000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3996000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4084000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7442000</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>47117000</v>
+      </c>
+      <c r="E43" s="3">
         <v>51999000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>44233000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63569000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>39132000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>37076000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>40625000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35497000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29408000</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26019000</v>
+      </c>
+      <c r="E44" s="3">
         <v>31894000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25258000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>38914000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24071000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>21117000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25223000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>21775000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>15822000</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22665000</v>
+      </c>
+      <c r="E45" s="3">
         <v>41955000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22417000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10787000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11862000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12805000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9364000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10516000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16900000</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>134115000</v>
+      </c>
+      <c r="E46" s="3">
         <v>165938000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>128765000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>91953000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>92689000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>97482000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>95404000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>86569000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>93358000</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>31814000</v>
+      </c>
+      <c r="E47" s="3">
         <v>31986000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>32757000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39632000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>32442000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>34409000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>42001000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>46948000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39844000</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>194835000</v>
+      </c>
+      <c r="E48" s="3">
         <v>198642000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>194932000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>420547000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>238349000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>223175000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>226380000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>236098000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>182838000</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26913000</v>
+      </c>
+      <c r="E49" s="3">
         <v>25701000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24693000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>45532000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23486000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23586000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24180000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>23967000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6283000</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1856,9 +1969,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1886,39 +2002,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18593000</v>
+      </c>
+      <c r="E52" s="3">
         <v>20757000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23232000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22914000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17370000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20542000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19132000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17693000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17834000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1946,39 +2068,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>406270000</v>
+      </c>
+      <c r="E54" s="3">
         <v>443024000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>404379000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>379268000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>404336000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>399194000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>407097000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>411275000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>340157000</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1991,8 +2119,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2005,188 +2134,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42110000</v>
+      </c>
+      <c r="E57" s="3">
         <v>51073000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>38929000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>70517000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32809000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33202000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35217000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30042000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>26298000</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9931000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9001000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8218000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>33798000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15064000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10134000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11795000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9484000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5530000</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43426000</v>
+      </c>
+      <c r="E59" s="3">
         <v>61237000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48400000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31301000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31751000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34477000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>32755000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34299000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39120000</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>95467000</v>
+      </c>
+      <c r="E60" s="3">
         <v>121311000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>95547000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>73708000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>79624000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>77813000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>79767000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>73825000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>70948000</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>71610000</v>
+      </c>
+      <c r="E61" s="3">
         <v>74794000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>80868000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>91115000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>81360000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>66690000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>73870000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>82992000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>52849000</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>50831000</v>
+      </c>
+      <c r="E62" s="3">
         <v>54322000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>52638000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>58212000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>52889000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>52157000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>55648000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>65947000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>52239000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2214,9 +2362,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2244,9 +2395,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2274,39 +2428,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>219663000</v>
+      </c>
+      <c r="E66" s="3">
         <v>252552000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>232413000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>223958000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>217860000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>200548000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>212741000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>224629000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>177281000</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,8 +2479,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2348,9 +2509,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2378,9 +2542,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2408,9 +2575,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2438,39 +2608,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>204757000</v>
+      </c>
+      <c r="E72" s="3">
         <v>208116000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>191427000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>180949000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>210901000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>221097000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>216467000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>214605000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>185240000</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2498,9 +2674,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2528,9 +2707,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,39 +2740,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>186607000</v>
+      </c>
+      <c r="E76" s="3">
         <v>190472000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>171966000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>155310000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>186476000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>198646000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>194356000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>186646000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>162876000</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2618,74 +2806,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19359000</v>
+      </c>
+      <c r="E81" s="3">
         <v>42309000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20101000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21680000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15842000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>23352000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12977000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4575000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1939000</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2698,38 +2895,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>31290000</v>
+      </c>
+      <c r="E83" s="3">
         <v>18529000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26921000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>52444000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>28701000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>22135000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26223000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24993000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26714000</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2757,9 +2958,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2787,9 +2991,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2817,9 +3024,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2847,9 +3057,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2877,39 +3090,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>54191000</v>
+      </c>
+      <c r="E89" s="3">
         <v>68414000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45104000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34105000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>42178000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>53085000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>35650000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>20615000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29810000</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2922,38 +3141,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22993000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22600000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19000000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16585000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22971000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23011000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20845000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22116000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26131000</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2981,9 +3204,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3011,39 +3237,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17734000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22448000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4761000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13278000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15779000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13659000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8029000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-30963000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22407000</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3056,38 +3288,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-8393000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-7405000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-6253000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-7424000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-15198000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-15675000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-10877000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-9677000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-9370000</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3115,9 +3351,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3145,9 +3384,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3175,97 +3417,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38235000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-41954000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-34664000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7224000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-35209000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-32548000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27086000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-771000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3812000</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>306000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-736000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-539000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>172000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>124000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-449000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>647000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1503000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1070000</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1472000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3276000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5140000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13775000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8686000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6429000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1182000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12622000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10145000</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
@@ -894,7 +894,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>7927000</v>
+        <v>7928000</v>
       </c>
       <c r="E14" s="3">
         <v>-3276000</v>
@@ -927,7 +927,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>23106000</v>
+        <v>23105000</v>
       </c>
       <c r="E15" s="3">
         <v>22393000</v>
@@ -1086,25 +1086,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>55065000</v>
+        <v>67826000</v>
       </c>
       <c r="E21" s="3">
-        <v>94481000</v>
+        <v>86089000</v>
       </c>
       <c r="F21" s="3">
-        <v>85429000</v>
+        <v>59906000</v>
       </c>
       <c r="G21" s="3">
-        <v>5294000</v>
+        <v>29037000</v>
       </c>
       <c r="H21" s="3">
-        <v>51460000</v>
+        <v>58026000</v>
       </c>
       <c r="I21" s="3">
-        <v>64518000</v>
+        <v>60430000</v>
       </c>
       <c r="J21" s="3">
-        <v>45949000</v>
+        <v>47179000</v>
       </c>
       <c r="K21" s="3">
         <v>32606000</v>

--- a/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
@@ -1658,7 +1658,7 @@
         <v>32441000</v>
       </c>
       <c r="G41" s="3">
-        <v>61375000</v>
+        <v>29545000</v>
       </c>
       <c r="H41" s="3">
         <v>14959000</v>
@@ -1724,7 +1724,7 @@
         <v>44233000</v>
       </c>
       <c r="G43" s="3">
-        <v>63569000</v>
+        <v>29944000</v>
       </c>
       <c r="H43" s="3">
         <v>39132000</v>
@@ -1757,7 +1757,7 @@
         <v>25258000</v>
       </c>
       <c r="G44" s="3">
-        <v>38914000</v>
+        <v>19457000</v>
       </c>
       <c r="H44" s="3">
         <v>24071000</v>
@@ -1790,7 +1790,7 @@
         <v>22417000</v>
       </c>
       <c r="G45" s="3">
-        <v>10787000</v>
+        <v>10788000</v>
       </c>
       <c r="H45" s="3">
         <v>11862000</v>
@@ -1823,7 +1823,7 @@
         <v>128765000</v>
       </c>
       <c r="G46" s="3">
-        <v>91953000</v>
+        <v>91954000</v>
       </c>
       <c r="H46" s="3">
         <v>92689000</v>
@@ -1856,7 +1856,7 @@
         <v>32757000</v>
       </c>
       <c r="G47" s="3">
-        <v>39632000</v>
+        <v>31991000</v>
       </c>
       <c r="H47" s="3">
         <v>32442000</v>
@@ -1889,7 +1889,7 @@
         <v>194932000</v>
       </c>
       <c r="G48" s="3">
-        <v>420547000</v>
+        <v>209700000</v>
       </c>
       <c r="H48" s="3">
         <v>238349000</v>
@@ -1922,7 +1922,7 @@
         <v>24693000</v>
       </c>
       <c r="G49" s="3">
-        <v>45532000</v>
+        <v>23197000</v>
       </c>
       <c r="H49" s="3">
         <v>23486000</v>
@@ -2021,7 +2021,7 @@
         <v>23232000</v>
       </c>
       <c r="G52" s="3">
-        <v>22914000</v>
+        <v>22913000</v>
       </c>
       <c r="H52" s="3">
         <v>17370000</v>
@@ -2150,7 +2150,7 @@
         <v>38929000</v>
       </c>
       <c r="G57" s="3">
-        <v>70517000</v>
+        <v>25945000</v>
       </c>
       <c r="H57" s="3">
         <v>32809000</v>
@@ -2183,7 +2183,7 @@
         <v>8218000</v>
       </c>
       <c r="G58" s="3">
-        <v>33798000</v>
+        <v>16899000</v>
       </c>
       <c r="H58" s="3">
         <v>15064000</v>
@@ -2216,7 +2216,7 @@
         <v>48400000</v>
       </c>
       <c r="G59" s="3">
-        <v>31301000</v>
+        <v>34412000</v>
       </c>
       <c r="H59" s="3">
         <v>31751000</v>
@@ -2315,7 +2315,7 @@
         <v>52638000</v>
       </c>
       <c r="G62" s="3">
-        <v>58212000</v>
+        <v>55908000</v>
       </c>
       <c r="H62" s="3">
         <v>52889000</v>

--- a/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
   <si>
     <t>SHEL</t>
   </si>
@@ -828,25 +828,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>3037000</v>
+        <v>1287000</v>
       </c>
       <c r="E12" s="3">
-        <v>2787000</v>
+        <v>1075000</v>
       </c>
       <c r="F12" s="3">
-        <v>2238000</v>
+        <v>815000</v>
       </c>
       <c r="G12" s="3">
-        <v>2654000</v>
+        <v>907000</v>
       </c>
       <c r="H12" s="3">
-        <v>3316000</v>
+        <v>962000</v>
       </c>
       <c r="I12" s="3">
-        <v>2326000</v>
+        <v>986000</v>
       </c>
       <c r="J12" s="3">
-        <v>2867000</v>
+        <v>922000</v>
       </c>
       <c r="K12" s="3">
         <v>3122000</v>
@@ -894,25 +894,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>7928000</v>
+        <v>3727000</v>
       </c>
       <c r="E14" s="3">
-        <v>-3276000</v>
+        <v>1778000</v>
       </c>
       <c r="F14" s="3">
-        <v>-1977000</v>
+        <v>-3464000</v>
       </c>
       <c r="G14" s="3">
-        <v>27177000</v>
+        <v>7022000</v>
       </c>
       <c r="H14" s="3">
-        <v>1073000</v>
+        <v>-1910000</v>
       </c>
       <c r="I14" s="3">
-        <v>-2834000</v>
+        <v>-2635000</v>
       </c>
       <c r="J14" s="3">
-        <v>1048000</v>
+        <v>-477000</v>
       </c>
       <c r="K14" s="3">
         <v>-1853000</v>
@@ -927,25 +927,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>23105000</v>
+        <v>28174000</v>
       </c>
       <c r="E15" s="3">
-        <v>22393000</v>
+        <v>18116000</v>
       </c>
       <c r="F15" s="3">
-        <v>22903000</v>
+        <v>25029000</v>
       </c>
       <c r="G15" s="3">
-        <v>24981000</v>
+        <v>45951000</v>
       </c>
       <c r="H15" s="3">
-        <v>25109000</v>
+        <v>29310000</v>
       </c>
       <c r="I15" s="3">
-        <v>21704000</v>
+        <v>21954000</v>
       </c>
       <c r="J15" s="3">
-        <v>22033000</v>
+        <v>26502000</v>
       </c>
       <c r="K15" s="3">
         <v>23091000</v>
@@ -972,25 +972,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>286345000</v>
+        <v>281222000</v>
       </c>
       <c r="E17" s="3">
-        <v>319196000</v>
+        <v>316434000</v>
       </c>
       <c r="F17" s="3">
-        <v>233676000</v>
+        <v>236349000</v>
       </c>
       <c r="G17" s="3">
-        <v>206284000</v>
+        <v>198765000</v>
       </c>
       <c r="H17" s="3">
-        <v>320130000</v>
+        <v>321322000</v>
       </c>
       <c r="I17" s="3">
-        <v>354827000</v>
+        <v>356560000</v>
       </c>
       <c r="J17" s="3">
-        <v>288933000</v>
+        <v>289080000</v>
       </c>
       <c r="K17" s="3">
         <v>230592000</v>
@@ -1005,25 +1005,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>30275000</v>
+        <v>35398000</v>
       </c>
       <c r="E18" s="3">
-        <v>62118000</v>
+        <v>64880000</v>
       </c>
       <c r="F18" s="3">
-        <v>27828000</v>
+        <v>25155000</v>
       </c>
       <c r="G18" s="3">
-        <v>-25741000</v>
+        <v>-18222000</v>
       </c>
       <c r="H18" s="3">
-        <v>24747000</v>
+        <v>23555000</v>
       </c>
       <c r="I18" s="3">
-        <v>33552000</v>
+        <v>31819000</v>
       </c>
       <c r="J18" s="3">
-        <v>16246000</v>
+        <v>16099000</v>
       </c>
       <c r="K18" s="3">
         <v>2999000</v>
@@ -1053,25 +1053,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>6261000</v>
+        <v>-3267000</v>
       </c>
       <c r="E20" s="3">
-        <v>5442000</v>
+        <v>-3632000</v>
       </c>
       <c r="F20" s="3">
-        <v>5157000</v>
+        <v>-4215000</v>
       </c>
       <c r="G20" s="3">
-        <v>2334000</v>
+        <v>-1665000</v>
       </c>
       <c r="H20" s="3">
-        <v>4578000</v>
+        <v>-3788000</v>
       </c>
       <c r="I20" s="3">
-        <v>4743000</v>
+        <v>-4036000</v>
       </c>
       <c r="J20" s="3">
-        <v>4710000</v>
+        <v>-4544000</v>
       </c>
       <c r="K20" s="3">
         <v>4614000</v>
@@ -1086,25 +1086,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>67826000</v>
+        <v>66839000</v>
       </c>
       <c r="E21" s="3">
-        <v>86089000</v>
+        <v>86628000</v>
       </c>
       <c r="F21" s="3">
-        <v>59906000</v>
+        <v>54399000</v>
       </c>
       <c r="G21" s="3">
-        <v>29037000</v>
+        <v>29394000</v>
       </c>
       <c r="H21" s="3">
-        <v>58026000</v>
+        <v>56653000</v>
       </c>
       <c r="I21" s="3">
-        <v>60430000</v>
+        <v>57809000</v>
       </c>
       <c r="J21" s="3">
-        <v>47179000</v>
+        <v>47145000</v>
       </c>
       <c r="K21" s="3">
         <v>32606000</v>
@@ -1119,25 +1119,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>3909000</v>
+        <v>4673000</v>
       </c>
       <c r="E22" s="3">
-        <v>2745000</v>
+        <v>3181000</v>
       </c>
       <c r="F22" s="3">
-        <v>3156000</v>
+        <v>3607000</v>
       </c>
       <c r="G22" s="3">
-        <v>3560000</v>
+        <v>4089000</v>
       </c>
       <c r="H22" s="3">
-        <v>3840000</v>
+        <v>4690000</v>
       </c>
       <c r="I22" s="3">
-        <v>2674000</v>
+        <v>3745000</v>
       </c>
       <c r="J22" s="3">
-        <v>2826000</v>
+        <v>4042000</v>
       </c>
       <c r="K22" s="3">
         <v>2007000</v>
@@ -1203,7 +1203,7 @@
         <v>11715000</v>
       </c>
       <c r="J24" s="3">
-        <v>2695000</v>
+        <v>4695000</v>
       </c>
       <c r="K24" s="3">
         <v>829000</v>
@@ -1269,7 +1269,7 @@
         <v>23906000</v>
       </c>
       <c r="J26" s="3">
-        <v>15435000</v>
+        <v>13435000</v>
       </c>
       <c r="K26" s="3">
         <v>4777000</v>
@@ -1302,7 +1302,7 @@
         <v>23352000</v>
       </c>
       <c r="J27" s="3">
-        <v>14977000</v>
+        <v>12977000</v>
       </c>
       <c r="K27" s="3">
         <v>4575000</v>
@@ -1349,26 +1349,26 @@
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-2000000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1449,25 +1449,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6261000</v>
+        <v>3267000</v>
       </c>
       <c r="E32" s="3">
-        <v>-5442000</v>
+        <v>3632000</v>
       </c>
       <c r="F32" s="3">
-        <v>-5157000</v>
+        <v>4215000</v>
       </c>
       <c r="G32" s="3">
-        <v>-2334000</v>
+        <v>1665000</v>
       </c>
       <c r="H32" s="3">
-        <v>-4578000</v>
+        <v>3788000</v>
       </c>
       <c r="I32" s="3">
-        <v>-4743000</v>
+        <v>4036000</v>
       </c>
       <c r="J32" s="3">
-        <v>-4710000</v>
+        <v>4544000</v>
       </c>
       <c r="K32" s="3">
         <v>-4614000</v>
@@ -1649,25 +1649,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>31724000</v>
+        <v>38774000</v>
       </c>
       <c r="E41" s="3">
-        <v>34943000</v>
+        <v>40246000</v>
       </c>
       <c r="F41" s="3">
-        <v>32441000</v>
+        <v>36970000</v>
       </c>
       <c r="G41" s="3">
-        <v>29545000</v>
+        <v>31830000</v>
       </c>
       <c r="H41" s="3">
-        <v>14959000</v>
+        <v>18055000</v>
       </c>
       <c r="I41" s="3">
-        <v>22829000</v>
+        <v>26741000</v>
       </c>
       <c r="J41" s="3">
-        <v>16196000</v>
+        <v>20312000</v>
       </c>
       <c r="K41" s="3">
         <v>14697000</v>
@@ -1682,25 +1682,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6590000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>5147000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>4416000</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>2220000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>2665000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>3655000</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>3996000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>4084000</v>
@@ -1781,25 +1781,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>22665000</v>
+        <v>16049000</v>
       </c>
       <c r="E45" s="3">
-        <v>41955000</v>
+        <v>27288000</v>
       </c>
       <c r="F45" s="3">
-        <v>22417000</v>
+        <v>13329000</v>
       </c>
       <c r="G45" s="3">
-        <v>10788000</v>
+        <v>7042000</v>
       </c>
       <c r="H45" s="3">
-        <v>11862000</v>
+        <v>7149000</v>
       </c>
       <c r="I45" s="3">
-        <v>12805000</v>
+        <v>7193000</v>
       </c>
       <c r="J45" s="3">
-        <v>9364000</v>
+        <v>5304000</v>
       </c>
       <c r="K45" s="3">
         <v>10516000</v>
@@ -1847,25 +1847,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>31814000</v>
+        <v>27703000</v>
       </c>
       <c r="E47" s="3">
-        <v>31986000</v>
+        <v>27226000</v>
       </c>
       <c r="F47" s="3">
-        <v>32757000</v>
+        <v>27212000</v>
       </c>
       <c r="G47" s="3">
-        <v>31991000</v>
+        <v>25673000</v>
       </c>
       <c r="H47" s="3">
-        <v>32442000</v>
+        <v>25797000</v>
       </c>
       <c r="I47" s="3">
-        <v>34409000</v>
+        <v>28403000</v>
       </c>
       <c r="J47" s="3">
-        <v>42001000</v>
+        <v>35149000</v>
       </c>
       <c r="K47" s="3">
         <v>46948000</v>
@@ -1922,7 +1922,7 @@
         <v>24693000</v>
       </c>
       <c r="G49" s="3">
-        <v>23197000</v>
+        <v>22710000</v>
       </c>
       <c r="H49" s="3">
         <v>23486000</v>
@@ -2012,25 +2012,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18593000</v>
+        <v>15218000</v>
       </c>
       <c r="E52" s="3">
-        <v>20757000</v>
+        <v>16612000</v>
       </c>
       <c r="F52" s="3">
-        <v>23232000</v>
+        <v>15066000</v>
       </c>
       <c r="G52" s="3">
-        <v>22913000</v>
+        <v>11540000</v>
       </c>
       <c r="H52" s="3">
-        <v>17370000</v>
+        <v>11963000</v>
       </c>
       <c r="I52" s="3">
-        <v>20542000</v>
+        <v>14451000</v>
       </c>
       <c r="J52" s="3">
-        <v>19132000</v>
+        <v>12193000</v>
       </c>
       <c r="K52" s="3">
         <v>17693000</v>
@@ -2141,25 +2141,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>42110000</v>
+        <v>34591000</v>
       </c>
       <c r="E57" s="3">
-        <v>51073000</v>
+        <v>42632000</v>
       </c>
       <c r="F57" s="3">
-        <v>38929000</v>
+        <v>34136000</v>
       </c>
       <c r="G57" s="3">
-        <v>25945000</v>
+        <v>22664000</v>
       </c>
       <c r="H57" s="3">
-        <v>32809000</v>
+        <v>29497000</v>
       </c>
       <c r="I57" s="3">
-        <v>33202000</v>
+        <v>30351000</v>
       </c>
       <c r="J57" s="3">
-        <v>35217000</v>
+        <v>33196000</v>
       </c>
       <c r="K57" s="3">
         <v>30042000</v>
@@ -2174,7 +2174,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9931000</v>
+        <v>10009000</v>
       </c>
       <c r="E58" s="3">
         <v>9001000</v>
@@ -2207,25 +2207,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>43426000</v>
+        <v>34309000</v>
       </c>
       <c r="E59" s="3">
-        <v>61237000</v>
+        <v>51132000</v>
       </c>
       <c r="F59" s="3">
-        <v>48400000</v>
+        <v>38234000</v>
       </c>
       <c r="G59" s="3">
-        <v>34412000</v>
+        <v>22186000</v>
       </c>
       <c r="H59" s="3">
-        <v>31751000</v>
+        <v>21123000</v>
       </c>
       <c r="I59" s="3">
-        <v>34477000</v>
+        <v>23017000</v>
       </c>
       <c r="J59" s="3">
-        <v>32755000</v>
+        <v>20568000</v>
       </c>
       <c r="K59" s="3">
         <v>34299000</v>
@@ -2273,7 +2273,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>71610000</v>
+        <v>71630000</v>
       </c>
       <c r="E61" s="3">
         <v>74794000</v>
@@ -2306,25 +2306,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>50831000</v>
+        <v>27915000</v>
       </c>
       <c r="E62" s="3">
-        <v>54322000</v>
+        <v>30840000</v>
       </c>
       <c r="F62" s="3">
-        <v>52638000</v>
+        <v>28766000</v>
       </c>
       <c r="G62" s="3">
-        <v>55908000</v>
+        <v>29840000</v>
       </c>
       <c r="H62" s="3">
-        <v>52889000</v>
+        <v>25350000</v>
       </c>
       <c r="I62" s="3">
-        <v>52157000</v>
+        <v>25667000</v>
       </c>
       <c r="J62" s="3">
-        <v>55648000</v>
+        <v>29394000</v>
       </c>
       <c r="K62" s="3">
         <v>65947000</v>
@@ -2438,25 +2438,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>219663000</v>
+        <v>217908000</v>
       </c>
       <c r="E66" s="3">
-        <v>252552000</v>
+        <v>250427000</v>
       </c>
       <c r="F66" s="3">
-        <v>232413000</v>
+        <v>229053000</v>
       </c>
       <c r="G66" s="3">
-        <v>223958000</v>
+        <v>220731000</v>
       </c>
       <c r="H66" s="3">
-        <v>217860000</v>
+        <v>213873000</v>
       </c>
       <c r="I66" s="3">
-        <v>200548000</v>
+        <v>196660000</v>
       </c>
       <c r="J66" s="3">
-        <v>212741000</v>
+        <v>209285000</v>
       </c>
       <c r="K66" s="3">
         <v>224629000</v>
@@ -2618,25 +2618,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>204757000</v>
+        <v>165915000</v>
       </c>
       <c r="E72" s="3">
-        <v>208116000</v>
+        <v>169482000</v>
       </c>
       <c r="F72" s="3">
-        <v>191427000</v>
+        <v>153026000</v>
       </c>
       <c r="G72" s="3">
-        <v>180949000</v>
+        <v>142616000</v>
       </c>
       <c r="H72" s="3">
-        <v>210901000</v>
+        <v>172431000</v>
       </c>
       <c r="I72" s="3">
-        <v>221097000</v>
+        <v>182606000</v>
       </c>
       <c r="J72" s="3">
-        <v>216467000</v>
+        <v>177645000</v>
       </c>
       <c r="K72" s="3">
         <v>214605000</v>
@@ -2902,25 +2902,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>31290000</v>
+        <v>21868000</v>
       </c>
       <c r="E83" s="3">
-        <v>18529000</v>
+        <v>21221000</v>
       </c>
       <c r="F83" s="3">
-        <v>26921000</v>
+        <v>21906000</v>
       </c>
       <c r="G83" s="3">
-        <v>52444000</v>
+        <v>24981000</v>
       </c>
       <c r="H83" s="3">
-        <v>28701000</v>
+        <v>25252000</v>
       </c>
       <c r="I83" s="3">
-        <v>22135000</v>
+        <v>21255000</v>
       </c>
       <c r="J83" s="3">
-        <v>26223000</v>
+        <v>22033000</v>
       </c>
       <c r="K83" s="3">
         <v>24993000</v>
@@ -3295,25 +3295,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8393000</v>
+        <v>8393000</v>
       </c>
       <c r="E96" s="3">
-        <v>-7405000</v>
+        <v>7405000</v>
       </c>
       <c r="F96" s="3">
-        <v>-6253000</v>
+        <v>6253000</v>
       </c>
       <c r="G96" s="3">
-        <v>-7424000</v>
+        <v>7424000</v>
       </c>
       <c r="H96" s="3">
-        <v>-15198000</v>
+        <v>15198000</v>
       </c>
       <c r="I96" s="3">
-        <v>-15675000</v>
+        <v>15675000</v>
       </c>
       <c r="J96" s="3">
-        <v>-10877000</v>
+        <v>10877000</v>
       </c>
       <c r="K96" s="3">
         <v>-9677000</v>

--- a/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
@@ -656,159 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>284312000</v>
+      </c>
+      <c r="E8" s="3">
         <v>316620000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>381314000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>261504000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>180543000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>344877000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>388379000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>305179000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>233591000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>264960000</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>211499000</v>
+      </c>
+      <c r="E9" s="3">
         <v>238123000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>284006000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>198734000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>141094000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>279421000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>321369000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>250099000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>191008000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>222739000</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>72813000</v>
+      </c>
+      <c r="E10" s="3">
         <v>78497000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>97308000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>62770000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>39449000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65456000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67010000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>55080000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>42583000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>42221000</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,41 +834,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1099000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1287000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1075000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>815000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>907000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>962000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>986000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>922000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3122000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6812000</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,75 +903,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4457000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3727000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1778000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3464000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7022000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1910000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2635000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-477000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1853000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5547000</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>24325000</v>
+      </c>
+      <c r="E15" s="3">
         <v>28174000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18116000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>25029000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>45951000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29310000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21954000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>26502000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>23091000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17707000</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -966,74 +991,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>281222000</v>
+        <v>250151000</v>
       </c>
       <c r="E17" s="3">
-        <v>316434000</v>
+        <v>281899000</v>
       </c>
       <c r="F17" s="3">
-        <v>236349000</v>
+        <v>316911000</v>
       </c>
       <c r="G17" s="3">
+        <v>236690000</v>
+      </c>
+      <c r="H17" s="3">
         <v>198765000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>321322000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>356560000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>289080000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>230592000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>264718000</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>35398000</v>
+        <v>34161000</v>
       </c>
       <c r="E18" s="3">
-        <v>64880000</v>
+        <v>34721000</v>
       </c>
       <c r="F18" s="3">
-        <v>25155000</v>
+        <v>64403000</v>
       </c>
       <c r="G18" s="3">
+        <v>24814000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-18222000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>23555000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>31819000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16099000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2999000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>242000</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1047,173 +1079,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-3267000</v>
+        <v>-2549000</v>
       </c>
       <c r="E20" s="3">
-        <v>-3632000</v>
+        <v>-3944000</v>
       </c>
       <c r="F20" s="3">
-        <v>-4215000</v>
+        <v>-4109000</v>
       </c>
       <c r="G20" s="3">
+        <v>-4556000</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1665000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3788000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4036000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4544000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4614000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2798000</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>61035000</v>
+      </c>
+      <c r="E21" s="3">
         <v>66839000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>86628000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>54399000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>29394000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>56653000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>57809000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47145000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32606000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29754000</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>4787000</v>
+      </c>
+      <c r="E22" s="3">
         <v>4673000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3181000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3607000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4089000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4690000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3745000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4042000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2007000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>993000</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>29921000</v>
+      </c>
+      <c r="E23" s="3">
         <v>32627000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>64815000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29829000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-26967000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25485000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>35621000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18130000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5606000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2047000</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>13401000</v>
+      </c>
+      <c r="E24" s="3">
         <v>12991000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21941000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9199000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5433000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9053000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11715000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4695000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>829000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-153000</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1244,75 +1292,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>16520000</v>
+      </c>
+      <c r="E26" s="3">
         <v>19636000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>42874000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20630000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21534000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16432000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23906000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13435000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4777000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2200000</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>16093000</v>
+      </c>
+      <c r="E27" s="3">
         <v>19359000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>42309000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20101000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21680000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15842000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23352000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12977000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4575000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1939000</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1343,9 +1400,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1370,15 +1430,18 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1409,9 +1472,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1442,75 +1508,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3267000</v>
+        <v>2549000</v>
       </c>
       <c r="E32" s="3">
-        <v>3632000</v>
+        <v>3944000</v>
       </c>
       <c r="F32" s="3">
-        <v>4215000</v>
+        <v>4109000</v>
       </c>
       <c r="G32" s="3">
+        <v>4556000</v>
+      </c>
+      <c r="H32" s="3">
         <v>1665000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3788000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4036000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4544000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4614000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2798000</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16093000</v>
+      </c>
+      <c r="E33" s="3">
         <v>19359000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>42309000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20101000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21680000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15842000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23352000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12977000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4575000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1939000</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1541,80 +1616,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16093000</v>
+      </c>
+      <c r="E35" s="3">
         <v>19359000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>42309000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20101000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21680000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15842000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23352000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12977000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4575000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1939000</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1712,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1643,41 +1728,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39110000</v>
+      </c>
+      <c r="E41" s="3">
         <v>38774000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>40246000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36970000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>31830000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18055000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26741000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20312000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14697000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23786000</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1703,245 +1792,269 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>4084000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7442000</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>45860000</v>
+      </c>
+      <c r="E43" s="3">
         <v>47117000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>51999000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>44233000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29944000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>39132000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>37076000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>40625000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>35497000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29408000</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23426000</v>
+      </c>
+      <c r="E44" s="3">
         <v>26019000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>31894000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25258000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19457000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>24071000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21117000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>25223000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>21775000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>15822000</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19530000</v>
+      </c>
+      <c r="E45" s="3">
         <v>16049000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27288000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13329000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7042000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7149000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7193000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5304000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10516000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16900000</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127926000</v>
+      </c>
+      <c r="E46" s="3">
         <v>134115000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>165938000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>128765000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>91954000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>92689000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>97482000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>95404000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>86569000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>93358000</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>25700000</v>
+      </c>
+      <c r="E47" s="3">
         <v>27703000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27226000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27212000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>25673000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>25797000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28403000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>35149000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>46948000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>39844000</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>185219000</v>
+      </c>
+      <c r="E48" s="3">
         <v>194835000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>198642000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>194932000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>209700000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>238349000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>223175000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>226380000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>236098000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>182838000</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25512000</v>
+      </c>
+      <c r="E49" s="3">
         <v>26913000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>25701000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24693000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22710000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23486000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23586000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24180000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23967000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6283000</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1972,9 +2085,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2005,42 +2121,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10375000</v>
+      </c>
+      <c r="E52" s="3">
         <v>15218000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16612000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15066000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11540000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11963000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14451000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12193000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17693000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17834000</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,42 +2193,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>387607000</v>
+      </c>
+      <c r="E54" s="3">
         <v>406270000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>443024000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>404379000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>379268000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>404336000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>399194000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>407097000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>411275000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>340157000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2120,8 +2248,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2135,206 +2264,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60693000</v>
+      </c>
+      <c r="E57" s="3">
         <v>34591000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>42632000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>34136000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22664000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29497000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30351000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33196000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30042000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>26298000</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11630000</v>
+      </c>
+      <c r="E58" s="3">
         <v>10009000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9001000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8218000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16899000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15064000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10134000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11795000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9484000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5530000</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22711000</v>
+      </c>
+      <c r="E59" s="3">
         <v>34309000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>51132000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>38234000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22186000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21123000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23017000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20568000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34299000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39120000</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>95034000</v>
+      </c>
+      <c r="E60" s="3">
         <v>95467000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>121311000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>95547000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>73708000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>79624000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>77813000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>79767000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>73825000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>70948000</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>65448000</v>
+      </c>
+      <c r="E61" s="3">
         <v>71630000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>74794000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>80868000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>91115000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>81360000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>66690000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>73870000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>82992000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>52849000</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26704000</v>
+      </c>
+      <c r="E62" s="3">
         <v>27915000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>30840000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28766000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>29840000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25350000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25667000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29394000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>65947000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>52239000</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2365,9 +2513,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2398,9 +2549,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2431,42 +2585,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>207443000</v>
+      </c>
+      <c r="E66" s="3">
         <v>217908000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>250427000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>229053000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>220731000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>213873000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>196660000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>209285000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>224629000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>177281000</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2480,8 +2640,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2512,9 +2673,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2545,9 +2709,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2578,9 +2745,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2611,42 +2781,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>158832000</v>
+      </c>
+      <c r="E72" s="3">
         <v>165915000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>169482000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>153026000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>142616000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>172431000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>182606000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>177645000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>214605000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>185240000</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2677,9 +2853,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2710,9 +2889,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2743,42 +2925,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>178303000</v>
+      </c>
+      <c r="E76" s="3">
         <v>186607000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>190472000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>171966000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>155310000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>186476000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>198646000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>194356000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>186646000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>162876000</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2809,80 +2997,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16093000</v>
+      </c>
+      <c r="E81" s="3">
         <v>19359000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>42309000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20101000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21680000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15842000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23352000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12977000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4575000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1939000</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,41 +3093,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22703000</v>
+      </c>
+      <c r="E83" s="3">
         <v>21868000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21221000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21906000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24981000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25252000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21255000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>22033000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24993000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26714000</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2961,9 +3162,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2994,9 +3198,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3027,9 +3234,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3060,9 +3270,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3093,42 +3306,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>54684000</v>
+      </c>
+      <c r="E89" s="3">
         <v>54191000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>68414000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>45104000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>34105000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>42178000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>53085000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>35650000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20615000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>29810000</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3142,41 +3361,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19601000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22993000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22600000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19000000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16585000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22971000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23011000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20845000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22116000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26131000</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3207,9 +3430,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3240,42 +3466,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15154000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17734000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22448000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4761000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13278000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15779000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13659000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8029000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30963000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22407000</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3289,41 +3521,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>8668000</v>
+      </c>
+      <c r="E96" s="3">
         <v>8393000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>7405000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>6253000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>7424000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>15198000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>15675000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>10877000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-9677000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-9370000</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3354,9 +3590,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3387,9 +3626,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3420,106 +3662,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38434000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38235000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-41954000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-34664000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7224000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-35209000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-32548000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27086000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-771000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3812000</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-761000</v>
+      </c>
+      <c r="E101" s="3">
         <v>306000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-736000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-539000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>172000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>124000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-449000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>647000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1503000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1070000</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1472000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3276000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5140000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13775000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8686000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6429000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1182000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12622000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10145000</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
@@ -913,13 +913,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>4457000</v>
+        <v>3748000</v>
       </c>
       <c r="E14" s="3">
-        <v>3727000</v>
+        <v>3636000</v>
       </c>
       <c r="F14" s="3">
-        <v>1778000</v>
+        <v>1706000</v>
       </c>
       <c r="G14" s="3">
         <v>-3464000</v>
@@ -949,13 +949,13 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>24325000</v>
+        <v>25034000</v>
       </c>
       <c r="E15" s="3">
-        <v>28174000</v>
+        <v>28265000</v>
       </c>
       <c r="F15" s="3">
-        <v>18116000</v>
+        <v>18188000</v>
       </c>
       <c r="G15" s="3">
         <v>25029000</v>
@@ -998,13 +998,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>250151000</v>
+        <v>250860000</v>
       </c>
       <c r="E17" s="3">
-        <v>281899000</v>
+        <v>281990000</v>
       </c>
       <c r="F17" s="3">
-        <v>316911000</v>
+        <v>316983000</v>
       </c>
       <c r="G17" s="3">
         <v>236690000</v>
@@ -1034,13 +1034,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>34161000</v>
+        <v>33452000</v>
       </c>
       <c r="E18" s="3">
-        <v>34721000</v>
+        <v>34630000</v>
       </c>
       <c r="F18" s="3">
-        <v>64403000</v>
+        <v>64331000</v>
       </c>
       <c r="G18" s="3">
         <v>24814000</v>
@@ -1086,7 +1086,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-2549000</v>
+        <v>-2550000</v>
       </c>
       <c r="E20" s="3">
         <v>-3944000</v>
@@ -1122,7 +1122,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>61035000</v>
+        <v>61036000</v>
       </c>
       <c r="E21" s="3">
         <v>66839000</v>
@@ -1194,7 +1194,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>29921000</v>
+        <v>29922000</v>
       </c>
       <c r="E23" s="3">
         <v>32627000</v>
@@ -1302,7 +1302,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>16520000</v>
+        <v>16521000</v>
       </c>
       <c r="E26" s="3">
         <v>19636000</v>
@@ -1338,7 +1338,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>16093000</v>
+        <v>16094000</v>
       </c>
       <c r="E27" s="3">
         <v>19359000</v>
@@ -1518,7 +1518,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2549000</v>
+        <v>2550000</v>
       </c>
       <c r="E32" s="3">
         <v>3944000</v>
@@ -1554,7 +1554,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>16093000</v>
+        <v>16094000</v>
       </c>
       <c r="E33" s="3">
         <v>19359000</v>
@@ -1626,7 +1626,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>16093000</v>
+        <v>16094000</v>
       </c>
       <c r="E35" s="3">
         <v>19359000</v>
@@ -1807,7 +1807,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>45860000</v>
+        <v>40147000</v>
       </c>
       <c r="E43" s="3">
         <v>47117000</v>
@@ -2131,7 +2131,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10375000</v>
+        <v>15520000</v>
       </c>
       <c r="E52" s="3">
         <v>15218000</v>
@@ -2203,7 +2203,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>387607000</v>
+        <v>387609000</v>
       </c>
       <c r="E54" s="3">
         <v>406270000</v>
@@ -2271,7 +2271,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>60693000</v>
+        <v>29767000</v>
       </c>
       <c r="E57" s="3">
         <v>34591000</v>
@@ -2307,7 +2307,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>11630000</v>
+        <v>11650000</v>
       </c>
       <c r="E58" s="3">
         <v>10009000</v>
@@ -2343,7 +2343,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>22711000</v>
+        <v>38672000</v>
       </c>
       <c r="E59" s="3">
         <v>34309000</v>
@@ -2415,7 +2415,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>65448000</v>
+        <v>65492000</v>
       </c>
       <c r="E61" s="3">
         <v>71630000</v>
@@ -2451,7 +2451,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>26704000</v>
+        <v>26658000</v>
       </c>
       <c r="E62" s="3">
         <v>27915000</v>
@@ -2595,7 +2595,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>207443000</v>
+        <v>207441000</v>
       </c>
       <c r="E66" s="3">
         <v>217908000</v>
@@ -2791,7 +2791,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>158832000</v>
+        <v>158834000</v>
       </c>
       <c r="E72" s="3">
         <v>165915000</v>
@@ -2935,7 +2935,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>178303000</v>
+        <v>178307000</v>
       </c>
       <c r="E76" s="3">
         <v>186607000</v>
@@ -3048,7 +3048,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>16093000</v>
+        <v>16094000</v>
       </c>
       <c r="E81" s="3">
         <v>19359000</v>
@@ -3100,13 +3100,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>22703000</v>
+        <v>21688000</v>
       </c>
       <c r="E83" s="3">
         <v>21868000</v>
       </c>
       <c r="F83" s="3">
-        <v>21221000</v>
+        <v>22393000</v>
       </c>
       <c r="G83" s="3">
         <v>21906000</v>
@@ -3316,7 +3316,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>54684000</v>
+        <v>54687000</v>
       </c>
       <c r="E89" s="3">
         <v>54191000</v>
@@ -3476,7 +3476,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-15154000</v>
+        <v>-15155000</v>
       </c>
       <c r="E94" s="3">
         <v>-17734000</v>
@@ -3672,7 +3672,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-38434000</v>
+        <v>-38435000</v>
       </c>
       <c r="E100" s="3">
         <v>-38235000</v>
@@ -3744,7 +3744,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>335000</v>
+        <v>336000</v>
       </c>
       <c r="E102" s="3">
         <v>-1472000</v>

--- a/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SHEL_YR_FIN.xlsx
@@ -656,171 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>266886000</v>
+      </c>
+      <c r="E8" s="3">
         <v>284312000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>316620000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>381314000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>261504000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>180543000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>344877000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>388379000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>305179000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>233591000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>264960000</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>199092000</v>
+      </c>
+      <c r="E9" s="3">
         <v>211499000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>238123000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>284006000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>198734000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>141094000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>279421000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>321369000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>250099000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>191008000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>222739000</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>67794000</v>
+      </c>
+      <c r="E10" s="3">
         <v>72813000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>78497000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>97308000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>62770000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>39449000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>65456000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67010000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>55080000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>42583000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>42221000</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,44 +847,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1170000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1099000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1287000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1075000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>815000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>907000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>962000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>986000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>922000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3122000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6812000</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,81 +922,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-938000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3748000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3636000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1706000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-3464000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7022000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1910000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2635000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-477000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1853000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5547000</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>23424000</v>
+      </c>
+      <c r="E15" s="3">
         <v>25034000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>28265000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18188000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>25029000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>45951000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29310000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21954000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>26502000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>23091000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17707000</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1017,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>237052000</v>
+      </c>
+      <c r="E17" s="3">
         <v>250860000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>281990000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>316983000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>236690000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>198765000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>321322000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>356560000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>289080000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>230592000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>264718000</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>29834000</v>
+      </c>
+      <c r="E18" s="3">
         <v>33452000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>34630000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>64331000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24814000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18222000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23555000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>31819000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16099000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2999000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>242000</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1080,188 +1112,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1613000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2550000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3944000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4109000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4556000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1665000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3788000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4036000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4544000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4614000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2798000</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>54871000</v>
+      </c>
+      <c r="E21" s="3">
         <v>61036000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>66839000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>86628000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>54399000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>29394000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>56653000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>57809000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47145000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32606000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29754000</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>4671000</v>
+      </c>
+      <c r="E22" s="3">
         <v>4787000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4673000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3181000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3607000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4089000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4690000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3745000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4042000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2007000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>993000</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>29756000</v>
+      </c>
+      <c r="E23" s="3">
         <v>29922000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32627000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>64815000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29829000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26967000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25485000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>35621000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18130000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5606000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2047000</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>11637000</v>
+      </c>
+      <c r="E24" s="3">
         <v>13401000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12991000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21941000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9199000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5433000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9053000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11715000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4695000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>829000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-153000</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1295,81 +1343,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>18119000</v>
+      </c>
+      <c r="E26" s="3">
         <v>16521000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19636000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>42874000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20630000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21534000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16432000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>23906000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13435000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4777000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2200000</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>17837000</v>
+      </c>
+      <c r="E27" s="3">
         <v>16094000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19359000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>42309000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20101000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21680000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15842000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>23352000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12977000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4575000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1939000</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1403,9 +1460,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1433,15 +1493,18 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1538,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1577,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1613000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2550000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3944000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4109000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4556000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1665000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3788000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4036000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4544000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4614000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2798000</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17837000</v>
+      </c>
+      <c r="E33" s="3">
         <v>16094000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19359000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>42309000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20101000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21680000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15842000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>23352000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12977000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4575000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1939000</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1694,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17837000</v>
+      </c>
+      <c r="E35" s="3">
         <v>16094000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19359000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>42309000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20101000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21680000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15842000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>23352000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12977000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4575000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1939000</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1797,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,44 +1814,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>30216000</v>
+      </c>
+      <c r="E41" s="3">
         <v>39110000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38774000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40246000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36970000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31830000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18055000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26741000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20312000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14697000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23786000</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1795,266 +1884,290 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>4084000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7442000</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40275000</v>
+      </c>
+      <c r="E43" s="3">
         <v>40147000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>47117000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>51999000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>44233000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29944000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39132000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>37076000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40625000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>35497000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29408000</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>22216000</v>
+      </c>
+      <c r="E44" s="3">
         <v>23426000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26019000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>31894000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>25258000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19457000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>24071000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>21117000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25223000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>21775000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15822000</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10144000</v>
+      </c>
+      <c r="E45" s="3">
         <v>19530000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16049000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27288000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13329000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7042000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7149000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7193000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5304000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10516000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16900000</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>107173000</v>
+      </c>
+      <c r="E46" s="3">
         <v>127926000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>134115000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>165938000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>128765000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>91954000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>92689000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>97482000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>95404000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>86569000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>93358000</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29332000</v>
+      </c>
+      <c r="E47" s="3">
         <v>25700000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27703000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27226000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27212000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>25673000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>25797000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28403000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>35149000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46948000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>39844000</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>185077000</v>
+      </c>
+      <c r="E48" s="3">
         <v>185219000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>194835000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>198642000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>194932000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>209700000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>238349000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>223175000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>226380000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>236098000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>182838000</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26672000</v>
+      </c>
+      <c r="E49" s="3">
         <v>25512000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26913000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25701000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24693000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22710000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23486000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>23586000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24180000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23967000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6283000</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2201,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,45 +2240,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13145000</v>
+      </c>
+      <c r="E52" s="3">
         <v>15520000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15218000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16612000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15066000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11540000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11963000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14451000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12193000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17693000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17834000</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2318,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>370350000</v>
+      </c>
+      <c r="E54" s="3">
         <v>387609000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>406270000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>443024000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>404379000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>379268000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>404336000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>399194000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>407097000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>411275000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>340157000</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2377,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,224 +2394,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28140000</v>
+      </c>
+      <c r="E57" s="3">
         <v>29767000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>34591000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>42632000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34136000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22664000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29497000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30351000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33196000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30042000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>26298000</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9147000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11650000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10009000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9001000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8218000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16899000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>15064000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10134000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11795000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9484000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5530000</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>31070000</v>
+      </c>
+      <c r="E59" s="3">
         <v>38672000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>34309000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>51132000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>38234000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22186000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21123000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23017000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20568000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34299000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39120000</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82415000</v>
+      </c>
+      <c r="E60" s="3">
         <v>95034000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>95467000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>121311000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>95547000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>73708000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>79624000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>77813000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>79767000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>73825000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>70948000</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>66541000</v>
+      </c>
+      <c r="E61" s="3">
         <v>65492000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>71630000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>74794000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>80868000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>91115000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>81360000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>66690000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>73870000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>82992000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>52849000</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26956000</v>
+      </c>
+      <c r="E62" s="3">
         <v>26658000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>27915000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>30840000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28766000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>29840000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25350000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25667000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29394000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>65947000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>52239000</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2664,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2552,9 +2703,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +2742,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>195031000</v>
+      </c>
+      <c r="E66" s="3">
         <v>207441000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>217908000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>250427000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>229053000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>220731000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>213873000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>196660000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>209285000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>224629000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>177281000</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +2801,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +2837,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,9 +2876,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2748,9 +2915,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,45 +2954,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>153528000</v>
+      </c>
+      <c r="E72" s="3">
         <v>158834000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>165915000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>169482000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>153026000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>142616000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>172431000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>182606000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>177645000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>214605000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>185240000</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3032,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3071,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3110,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>174392000</v>
+      </c>
+      <c r="E76" s="3">
         <v>178307000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>186607000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>190472000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>171966000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>155310000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>186476000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>198646000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>194356000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>186646000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>162876000</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3188,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17837000</v>
+      </c>
+      <c r="E81" s="3">
         <v>16094000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19359000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>42309000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20101000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21680000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15842000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>23352000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12977000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4575000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1939000</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3291,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21030000</v>
+      </c>
+      <c r="E83" s="3">
         <v>21688000</v>
       </c>
-      <c r="E83" s="3">
-        <v>21868000</v>
-      </c>
       <c r="F83" s="3">
+        <v>23105000</v>
+      </c>
+      <c r="G83" s="3">
         <v>22393000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21906000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24981000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25252000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21255000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>22033000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24993000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26714000</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3366,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3405,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3444,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3483,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3522,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>42863000</v>
+      </c>
+      <c r="E89" s="3">
         <v>54687000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>54191000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>68414000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>45104000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>34105000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>42178000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>53085000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35650000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>20615000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>29810000</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +3581,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18947000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19601000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22993000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22600000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19000000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16585000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-22971000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23011000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20845000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22116000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26131000</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +3656,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +3695,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16811000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15155000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17734000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22448000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4761000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13278000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15779000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13659000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8029000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30963000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22407000</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,44 +3754,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>8472000</v>
+      </c>
+      <c r="E96" s="3">
         <v>8668000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>8393000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>7405000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>6253000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>7424000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>15198000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>15675000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>10877000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-9677000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-9370000</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +3829,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +3868,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,115 +3907,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-35812000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38435000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-38235000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-41954000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-34664000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7224000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-35209000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-32548000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27086000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-771000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3812000</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-761000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>306000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-736000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-539000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>172000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>124000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-449000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>647000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1503000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1070000</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8894000</v>
+      </c>
+      <c r="E102" s="3">
         <v>336000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1472000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3276000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5140000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13775000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8686000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6429000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1182000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12622000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10145000</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
